--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91683</v>
+        <v>91688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001002</v>
       </c>
       <c r="B3" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91695</v>
+        <v>91698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001002</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91701</v>
+        <v>91708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001002</v>
       </c>
       <c r="B3" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91708</v>
+        <v>91715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91715</v>
+        <v>91717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001002</v>
       </c>
       <c r="B3" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91717</v>
+        <v>91726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91726</v>
+        <v>91727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91727</v>
+        <v>91730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001002</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91730</v>
+        <v>91732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129001002</v>
       </c>
       <c r="B3" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91732</v>
+        <v>91736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91736</v>
+        <v>91737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45828-2025 artfynd.xlsx
+++ b/artfynd/A 45828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001003</v>
       </c>
       <c r="B2" t="n">
-        <v>91737</v>
+        <v>91740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
